--- a/03_IE_tasks/data/related/outcomes_endpoints/Enpoints_emborgEvaluationAnimalModels2004.xlsx
+++ b/03_IE_tasks/data/related/outcomes_endpoints/Enpoints_emborgEvaluationAnimalModels2004.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sdoneva/Documents/Work/In Progress/PhD/PhD Projects/In Progress/Preclinical_Pipeline/03_IE_tasks/data/related/outcomes_endpoints/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BD0007E-5944-2745-961F-264717D746BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B58B0557-AB8C-0549-B636-3CF449A8372E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="35120" yWindow="4060" windowWidth="27640" windowHeight="24740" xr2:uid="{CA3C7809-DF78-FC4B-BA4A-BF2403FDEDDF}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17740" xr2:uid="{CA3C7809-DF78-FC4B-BA4A-BF2403FDEDDF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="86">
   <si>
     <t>Test Name</t>
   </si>
@@ -53,9 +53,6 @@
     <t>Net full turns (ipsilateral vs. contralateral) per minute over 90 min after 2.5 mg/kg i.p. amphetamine</t>
   </si>
   <si>
-    <t>Behavioral</t>
-  </si>
-  <si>
     <t>Apomorphine‐induced rotation</t>
   </si>
   <si>
@@ -104,9 +101,6 @@
     <t>Implanted‐transmitter measures: spontaneous activity, core temperature, respiratory rate, BP</t>
   </si>
   <si>
-    <t>Physiological &amp; Metabolic</t>
-  </si>
-  <si>
     <t>Personal activity monitor (PAM)</t>
   </si>
   <si>
@@ -227,9 +221,6 @@
     <t>Plasma prolactin and melatonin concentrations over 24 h</t>
   </si>
   <si>
-    <t>Imaging &amp; Morphology</t>
-  </si>
-  <si>
     <t>Macro‐anatomical structure, lesion location/volume, BBB integrity, edema</t>
   </si>
   <si>
@@ -291,6 +282,18 @@
   </si>
   <si>
     <t>Magnetic resonance imaging (MRI)</t>
+  </si>
+  <si>
+    <t>Behaviour</t>
+  </si>
+  <si>
+    <t>Physiology</t>
+  </si>
+  <si>
+    <t>Imaging</t>
+  </si>
+  <si>
+    <t>Histology</t>
   </si>
 </sst>
 </file>
@@ -705,425 +708,425 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
       <c r="C3" t="s">
-        <v>5</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
       <c r="C4" t="s">
-        <v>5</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
         <v>10</v>
       </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
       <c r="C5" t="s">
-        <v>5</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
         <v>12</v>
       </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
       <c r="C6" t="s">
-        <v>5</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
         <v>14</v>
       </c>
-      <c r="B7" t="s">
-        <v>15</v>
-      </c>
       <c r="C7" t="s">
-        <v>5</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
         <v>16</v>
       </c>
-      <c r="B8" t="s">
-        <v>17</v>
-      </c>
       <c r="C8" t="s">
-        <v>5</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" t="s">
         <v>18</v>
       </c>
-      <c r="B9" t="s">
-        <v>19</v>
-      </c>
       <c r="C9" t="s">
-        <v>5</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
         <v>20</v>
       </c>
-      <c r="B10" t="s">
-        <v>21</v>
-      </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>5</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>5</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>5</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C14" t="s">
-        <v>5</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>5</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>5</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>5</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B18" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>5</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B19" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>5</v>
+        <v>82</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>5</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B21" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C21" t="s">
-        <v>5</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B22" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C22" t="s">
-        <v>5</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B23" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C23" t="s">
-        <v>5</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B24" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C24" t="s">
-        <v>22</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B25" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C25" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B26" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C26" t="s">
-        <v>5</v>
+        <v>82</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B27" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C27" t="s">
-        <v>5</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B28" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C28" t="s">
-        <v>22</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B29" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C29" t="s">
-        <v>22</v>
+        <v>83</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B30" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C30" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
+        <v>81</v>
+      </c>
+      <c r="B31" t="s">
+        <v>61</v>
+      </c>
+      <c r="C31" t="s">
         <v>84</v>
-      </c>
-      <c r="B31" t="s">
-        <v>64</v>
-      </c>
-      <c r="C31" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B32" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C32" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B33" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C33" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B34" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C34" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B35" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C35" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B36" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C36" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B37" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C37" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B38" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C38" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B39" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C39" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B40" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C40" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
